--- a/04_DESIGN_TABLES/DesignTable_2504.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2504.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -947,6 +947,27 @@
           <t>2504-04-04-FG</t>
         </is>
       </c>
+      <c r="B10" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4375</v>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>2504-04-04-FG</t>
@@ -954,17 +975,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2504-04-04 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>2026-10-02 new master (JIC-TEES): legs / hex / bores from the OMi dimension file (OMi M 1 / M 2 / Hex Flat / Side 1 ID / Side 2 ID = legs of ends 1 / 2, body hex, bores (Brennan TFA catalog p26 drawing M1 / M2 / Y / B1 / B2; Brennan 2504-08-08-FG STEP: tips 0.980 / 0.980, A/F 0.750, bores 0.391 = OMi row 784)); OMi = Brennan data (Brennan catalog TFA p26 (MJ-MJ 45 DEG ELBOW) prints the same values) = ONE source -&gt; ASSUMED; thread majors from the OMi thread callouts;  | previous: OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2504-04-04 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2504-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>2026-10-02 (JIC-TEES): MISSING -&gt; ASSUMED, every cell sourced (staged_sources.csv); single source family (OMi = Brennan) - not released for production | previous: BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2504-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -984,6 +1005,27 @@
           <t>2504-06-06-FG</t>
         </is>
       </c>
+      <c r="B11" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.5625</v>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>2504-06-06-FG</t>
@@ -991,17 +1033,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2504-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>2026-10-02 new master (JIC-TEES): legs / hex / bores from the OMi dimension file (OMi M 1 / M 2 / Hex Flat / Side 1 ID / Side 2 ID = legs of ends 1 / 2, body hex, bores (Brennan TFA catalog p26 drawing M1 / M2 / Y / B1 / B2; Brennan 2504-08-08-FG STEP: tips 0.980 / 0.980, A/F 0.750, bores 0.391 = OMi row 784)); OMi = Brennan data (Brennan catalog TFA p26 (MJ-MJ 45 DEG ELBOW) prints the same values) = ONE source -&gt; ASSUMED; thread majors from the OMi thread callouts;  | previous: OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2504-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2504-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>2026-10-02 (JIC-TEES): MISSING -&gt; ASSUMED, every cell sourced (staged_sources.csv); single source family (OMi = Brennan) - not released for production | previous: BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2504-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1021,6 +1063,27 @@
           <t>2504-08-08-FG</t>
         </is>
       </c>
+      <c r="B12" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>2504-08-08-FG</t>
@@ -1028,17 +1091,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2504-08-08 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>2026-10-02 new master (JIC-TEES): legs / hex / bores from the OMi dimension file (OMi M 1 / M 2 / Hex Flat / Side 1 ID / Side 2 ID = legs of ends 1 / 2, body hex, bores (Brennan TFA catalog p26 drawing M1 / M2 / Y / B1 / B2; Brennan 2504-08-08-FG STEP: tips 0.980 / 0.980, A/F 0.750, bores 0.391 = OMi row 784)); OMi = Brennan data (Brennan catalog TFA p26 (MJ-MJ 45 DEG ELBOW) prints the same values) = ONE source -&gt; ASSUMED; thread majors from the OMi thread callouts;  | previous: OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2504-08-08 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2504-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>2026-10-02 (JIC-TEES): MISSING -&gt; ASSUMED, every cell sourced (staged_sources.csv); single source family (OMi = Brennan) - not released for production | previous: BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2504-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1058,6 +1121,27 @@
           <t>2504-12-12-FG</t>
         </is>
       </c>
+      <c r="B13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.0625</v>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>2504-12-12-FG</t>
@@ -1065,17 +1149,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2504-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>2026-10-02 new master (JIC-TEES): legs / hex / bores from the OMi dimension file (OMi M 1 / M 2 / Hex Flat / Side 1 ID / Side 2 ID = legs of ends 1 / 2, body hex, bores (Brennan TFA catalog p26 drawing M1 / M2 / Y / B1 / B2; Brennan 2504-08-08-FG STEP: tips 0.980 / 0.980, A/F 0.750, bores 0.391 = OMi row 784)); OMi = Brennan data (Brennan catalog TFA p26 (MJ-MJ 45 DEG ELBOW) prints the same values) = ONE source -&gt; ASSUMED; thread majors from the OMi thread callouts;  | previous: OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2504-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2504-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>2026-10-02 (JIC-TEES): MISSING -&gt; ASSUMED, every cell sourced (staged_sources.csv); single source family (OMi = Brennan) - not released for production | previous: BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2504-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_2504.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2504.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,6 +499,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1170,6 +1175,69 @@
       <c r="P13" t="inlineStr">
         <is>
           <t>2504-12-12-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2504-16-16-FG</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2504-16-16-FG</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; legs / flats / bores: OMi WebsitePartsInfo2026 Items M 1 / M 2 / Hex Flat / Side 1 ID / Side 2 ID (= Brennan TFA p.26, one source); JIC ends MS33656J</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; legs / flats / bores from OMi Items (= Brennan TFA p.26, one source)</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2504-16-16-FG</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>OMI</t>
         </is>
       </c>
     </row>
